--- a/public/report_templates/caja/reportes/vchComision.xlsx
+++ b/public/report_templates/caja/reportes/vchComision.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredipymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BC3710-9080-41B4-87B9-86B791387812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03DCFE1-3D05-414A-A2CD-C0297EEB961F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
   <sheets>
     <sheet name="vchComision" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -74,10 +74,7 @@
     <t xml:space="preserve">¿Alguna duda?, llámanos o escribenos al whatsapp </t>
   </si>
   <si>
-    <t>GRUPO CREDIPYME</t>
-  </si>
-  <si>
-    <t>RUC: 20611432616</t>
+    <t>CREDIPYME HUANCA SAC</t>
   </si>
 </sst>
 </file>
@@ -540,9 +537,7 @@
       <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>14</v>
-      </c>
+      <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
     </row>

--- a/public/report_templates/caja/reportes/vchComision.xlsx
+++ b/public/report_templates/caja/reportes/vchComision.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\CredypymeApp\public\report_templates\caja\reportes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\CredypymeApp\public\report_templates\caja\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03DCFE1-3D05-414A-A2CD-C0297EEB961F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9138C495-457A-435F-9356-3022E6C41B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{9AFC928B-410F-4A53-A090-F50511B27738}"/>
   </bookViews>
   <sheets>
     <sheet name="vchComision" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -74,7 +74,10 @@
     <t xml:space="preserve">¿Alguna duda?, llámanos o escribenos al whatsapp </t>
   </si>
   <si>
-    <t>CREDIPYME HUANCA SAC</t>
+    <t>CREDIPYME HUANCA S.A.C</t>
+  </si>
+  <si>
+    <t>RUC: 20614827239</t>
   </si>
 </sst>
 </file>
@@ -537,7 +540,9 @@
       <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
     </row>
